--- a/output/Princeton/Cash_Reconciliation_Report_Database.xlsx
+++ b/output/Princeton/Cash_Reconciliation_Report_Database.xlsx
@@ -423,10 +423,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Princ DEP Sterling X2316:</v>
+        <v>RFMS Account # ****5936:</v>
       </c>
       <c r="B3" t="str">
-        <v>$962,061.64</v>
+        <v>$16,087.90</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -434,10 +434,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Princ GOV Sterling X2315:</v>
+        <v>Princ PAY Webster X6747:</v>
       </c>
       <c r="B4" t="str">
-        <v>$742,666.62</v>
+        <v>$438,840.01</v>
       </c>
       <c r="C4" t="str">
         <v/>
@@ -445,10 +445,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Princ OPE Sterling X2312:</v>
+        <v>Princ GOV Sterling X2315:</v>
       </c>
       <c r="B5" t="str">
-        <v>$26,868,965.08</v>
+        <v>$742,666.62</v>
       </c>
       <c r="C5" t="str">
         <v/>
@@ -456,10 +456,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Princ PAY Webster X6747:</v>
+        <v>Princ DEP Sterling X2316:</v>
       </c>
       <c r="B6" t="str">
-        <v>$438,840.01</v>
+        <v>$962,061.64</v>
       </c>
       <c r="C6" t="str">
         <v/>
@@ -467,10 +467,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>RFMS Account # ****5936:</v>
+        <v>Princ OPE Sterling X2312:</v>
       </c>
       <c r="B7" t="str">
-        <v>$16,087.90</v>
+        <v>$26,868,965.08</v>
       </c>
       <c r="C7" t="str">
         <v/>
@@ -539,7 +539,7 @@
         <v>ACH</v>
       </c>
       <c r="C13" t="str">
-        <v>$1,170.00</v>
+        <v>$59.49</v>
       </c>
     </row>
     <row r="14">
@@ -550,7 +550,7 @@
         <v>ACH</v>
       </c>
       <c r="C14" t="str">
-        <v>$583.00</v>
+        <v>$215.00</v>
       </c>
     </row>
     <row r="15">
@@ -561,7 +561,7 @@
         <v>ACH</v>
       </c>
       <c r="C15" t="str">
-        <v>$500.00</v>
+        <v>$276.06</v>
       </c>
     </row>
     <row r="16">
@@ -572,7 +572,7 @@
         <v>ACH</v>
       </c>
       <c r="C16" t="str">
-        <v>$1,494.00</v>
+        <v>$500.00</v>
       </c>
     </row>
     <row r="17">
@@ -583,7 +583,7 @@
         <v>ACH</v>
       </c>
       <c r="C17" t="str">
-        <v>$17,902.50</v>
+        <v>$583.00</v>
       </c>
     </row>
     <row r="18">
@@ -594,7 +594,7 @@
         <v>ACH</v>
       </c>
       <c r="C18" t="str">
-        <v>$215.00</v>
+        <v>$663.00</v>
       </c>
     </row>
     <row r="19">
@@ -605,7 +605,7 @@
         <v>ACH</v>
       </c>
       <c r="C19" t="str">
-        <v>$9,820.36</v>
+        <v>$1,159.00</v>
       </c>
     </row>
     <row r="20">
@@ -616,7 +616,7 @@
         <v>ACH</v>
       </c>
       <c r="C20" t="str">
-        <v>$8,951.25</v>
+        <v>$1,170.00</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>ACH</v>
       </c>
       <c r="C21" t="str">
-        <v>$4,400.00</v>
+        <v>$1,186.00</v>
       </c>
     </row>
     <row r="22">
@@ -638,7 +638,7 @@
         <v>ACH</v>
       </c>
       <c r="C22" t="str">
-        <v>$8,951.25</v>
+        <v>$1,494.00</v>
       </c>
     </row>
     <row r="23">
@@ -649,7 +649,7 @@
         <v>ACH</v>
       </c>
       <c r="C23" t="str">
-        <v>$8,951.25</v>
+        <v>$2,537.94</v>
       </c>
     </row>
     <row r="24">
@@ -660,7 +660,7 @@
         <v>ACH</v>
       </c>
       <c r="C24" t="str">
-        <v>$59.49</v>
+        <v>$4,400.00</v>
       </c>
     </row>
     <row r="25">
@@ -671,7 +671,7 @@
         <v>ACH</v>
       </c>
       <c r="C25" t="str">
-        <v>$2,537.94</v>
+        <v>$8,951.25</v>
       </c>
     </row>
     <row r="26">
@@ -682,7 +682,7 @@
         <v>ACH</v>
       </c>
       <c r="C26" t="str">
-        <v>$276.06</v>
+        <v>$8,951.25</v>
       </c>
     </row>
     <row r="27">
@@ -693,7 +693,7 @@
         <v>ACH</v>
       </c>
       <c r="C27" t="str">
-        <v>$1,186.00</v>
+        <v>$8,951.25</v>
       </c>
     </row>
     <row r="28">
@@ -704,7 +704,7 @@
         <v>ACH</v>
       </c>
       <c r="C28" t="str">
-        <v>$663.00</v>
+        <v>$9,820.36</v>
       </c>
     </row>
     <row r="29">
@@ -715,7 +715,7 @@
         <v>ACH</v>
       </c>
       <c r="C29" t="str">
-        <v>$1,159.00</v>
+        <v>$17,902.50</v>
       </c>
     </row>
     <row r="30">
